--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1428"/>
+  <dimension ref="A1:C1457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21473,6 +21473,325 @@
         <v>385</v>
       </c>
     </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr"/>
+      <c r="C1429" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr"/>
+      <c r="C1430" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr"/>
+      <c r="C1431" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr"/>
+      <c r="C1432" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr"/>
+      <c r="C1433" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr"/>
+      <c r="C1434" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr"/>
+      <c r="C1435" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr"/>
+      <c r="C1436" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr"/>
+      <c r="C1437" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr"/>
+      <c r="C1438" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr"/>
+      <c r="C1439" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr"/>
+      <c r="C1440" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr"/>
+      <c r="C1441" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr"/>
+      <c r="C1442" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr"/>
+      <c r="C1443" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr"/>
+      <c r="C1444" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr"/>
+      <c r="C1445" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr"/>
+      <c r="C1446" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr"/>
+      <c r="C1447" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr"/>
+      <c r="C1448" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr"/>
+      <c r="C1449" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr"/>
+      <c r="C1450" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr"/>
+      <c r="C1451" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr"/>
+      <c r="C1452" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr"/>
+      <c r="C1453" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr"/>
+      <c r="C1454" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr"/>
+      <c r="C1455" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr"/>
+      <c r="C1456" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr"/>
+      <c r="C1457" t="n">
+        <v>386</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1457"/>
+  <dimension ref="A1:C1581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21792,6 +21792,1507 @@
         <v>386</v>
       </c>
     </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr"/>
+      <c r="C1482" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr"/>
+      <c r="C1483" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr"/>
+      <c r="C1484" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr"/>
+      <c r="C1485" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr"/>
+      <c r="C1486" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr"/>
+      <c r="C1487" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr"/>
+      <c r="C1488" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr"/>
+      <c r="C1489" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr"/>
+      <c r="C1490" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr"/>
+      <c r="C1491" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr"/>
+      <c r="C1492" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr"/>
+      <c r="C1493" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr"/>
+      <c r="C1494" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr"/>
+      <c r="C1495" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr"/>
+      <c r="C1496" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr"/>
+      <c r="C1497" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr"/>
+      <c r="C1498" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr"/>
+      <c r="C1499" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr"/>
+      <c r="C1500" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr"/>
+      <c r="C1501" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr"/>
+      <c r="C1502" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr"/>
+      <c r="C1503" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr"/>
+      <c r="C1504" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr"/>
+      <c r="C1505" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr"/>
+      <c r="C1509" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr"/>
+      <c r="C1510" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr"/>
+      <c r="C1511" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr"/>
+      <c r="C1512" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr"/>
+      <c r="C1513" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr"/>
+      <c r="C1514" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr"/>
+      <c r="C1515" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr"/>
+      <c r="C1516" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr"/>
+      <c r="C1517" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr"/>
+      <c r="C1518" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr"/>
+      <c r="C1519" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr"/>
+      <c r="C1520" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr"/>
+      <c r="C1521" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr"/>
+      <c r="C1522" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr"/>
+      <c r="C1523" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr"/>
+      <c r="C1524" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr"/>
+      <c r="C1525" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr"/>
+      <c r="C1526" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr"/>
+      <c r="C1527" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr"/>
+      <c r="C1528" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr"/>
+      <c r="C1529" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr"/>
+      <c r="C1530" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr"/>
+      <c r="C1531" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr"/>
+      <c r="C1532" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr"/>
+      <c r="C1533" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr"/>
+      <c r="C1534" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr"/>
+      <c r="C1535" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr"/>
+      <c r="C1536" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr"/>
+      <c r="C1537" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr"/>
+      <c r="C1538" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr"/>
+      <c r="C1539" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr"/>
+      <c r="C1540" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr"/>
+      <c r="C1541" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr"/>
+      <c r="C1542" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr"/>
+      <c r="C1543" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr"/>
+      <c r="C1544" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr"/>
+      <c r="C1545" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr"/>
+      <c r="C1546" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr"/>
+      <c r="C1547" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr"/>
+      <c r="C1548" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr"/>
+      <c r="C1549" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr"/>
+      <c r="C1550" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr"/>
+      <c r="C1551" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr"/>
+      <c r="C1552" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr"/>
+      <c r="C1553" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr"/>
+      <c r="C1554" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr"/>
+      <c r="C1555" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr"/>
+      <c r="C1556" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr"/>
+      <c r="C1558" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr"/>
+      <c r="C1559" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr"/>
+      <c r="C1560" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr"/>
+      <c r="C1561" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr"/>
+      <c r="C1562" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr"/>
+      <c r="C1563" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr"/>
+      <c r="C1564" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr"/>
+      <c r="C1565" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr"/>
+      <c r="C1566" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr"/>
+      <c r="C1567" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr"/>
+      <c r="C1568" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr"/>
+      <c r="C1569" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr"/>
+      <c r="C1570" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr"/>
+      <c r="C1571" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr"/>
+      <c r="C1572" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr"/>
+      <c r="C1573" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr"/>
+      <c r="C1574" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr"/>
+      <c r="C1575" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr"/>
+      <c r="C1576" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr"/>
+      <c r="C1577" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr"/>
+      <c r="C1578" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr"/>
+      <c r="C1579" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr"/>
+      <c r="C1580" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr"/>
+      <c r="C1581" t="n">
+        <v>390</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1581"/>
+  <dimension ref="A1:C1605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23293,6 +23293,270 @@
         <v>390</v>
       </c>
     </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr"/>
+      <c r="C1582" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr"/>
+      <c r="C1583" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr"/>
+      <c r="C1584" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr"/>
+      <c r="C1585" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr"/>
+      <c r="C1586" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr"/>
+      <c r="C1587" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr"/>
+      <c r="C1588" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr"/>
+      <c r="C1589" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr"/>
+      <c r="C1590" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr"/>
+      <c r="C1591" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr"/>
+      <c r="C1592" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr"/>
+      <c r="C1593" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr"/>
+      <c r="C1594" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr"/>
+      <c r="C1595" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr"/>
+      <c r="C1596" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr"/>
+      <c r="C1597" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr"/>
+      <c r="C1598" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr"/>
+      <c r="C1599" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr"/>
+      <c r="C1600" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr"/>
+      <c r="C1601" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr"/>
+      <c r="C1602" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr"/>
+      <c r="C1603" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr"/>
+      <c r="C1604" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr"/>
+      <c r="C1605" t="n">
+        <v>391</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1605"/>
+  <dimension ref="A1:C1661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23557,6 +23557,670 @@
         <v>391</v>
       </c>
     </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1606" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1607" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bauer t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1608" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bauer t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1609" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">winter n 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1610" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lechner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1611" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">winter n 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1612" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lechner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1613" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr"/>
+      <c r="C1614" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr"/>
+      <c r="C1615" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr"/>
+      <c r="C1616" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr"/>
+      <c r="C1617" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr"/>
+      <c r="C1618" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr"/>
+      <c r="C1619" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr"/>
+      <c r="C1620" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr"/>
+      <c r="C1621" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr"/>
+      <c r="C1622" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr"/>
+      <c r="C1623" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr"/>
+      <c r="C1624" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr"/>
+      <c r="C1625" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr"/>
+      <c r="C1626" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr"/>
+      <c r="C1627" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr"/>
+      <c r="C1628" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr"/>
+      <c r="C1629" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr"/>
+      <c r="C1630" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr"/>
+      <c r="C1631" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr"/>
+      <c r="C1632" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr"/>
+      <c r="C1633" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr"/>
+      <c r="C1634" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr"/>
+      <c r="C1635" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr"/>
+      <c r="C1636" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr"/>
+      <c r="C1639" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr"/>
+      <c r="C1640" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr"/>
+      <c r="C1641" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr"/>
+      <c r="C1642" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr"/>
+      <c r="C1643" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr"/>
+      <c r="C1644" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr"/>
+      <c r="C1645" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr"/>
+      <c r="C1646" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr"/>
+      <c r="C1647" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr"/>
+      <c r="C1648" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr"/>
+      <c r="C1649" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr"/>
+      <c r="C1650" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr"/>
+      <c r="C1651" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr"/>
+      <c r="C1652" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr"/>
+      <c r="C1653" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr"/>
+      <c r="C1654" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr"/>
+      <c r="C1655" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr"/>
+      <c r="C1656" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr"/>
+      <c r="C1657" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr"/>
+      <c r="C1658" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr"/>
+      <c r="C1659" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr"/>
+      <c r="C1660" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr"/>
+      <c r="C1661" t="n">
+        <v>393</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1661"/>
+  <dimension ref="A1:C1686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24221,6 +24221,376 @@
         <v>393</v>
       </c>
     </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weisbach e 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ernst abbe sportfeld
+  jena </t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr"/>
+      <c r="C1675" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>AgnJojCs</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>CCww5Qfo</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr"/>
+      <c r="C1679" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr"/>
+      <c r="C1680" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr"/>
+      <c r="C1681" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1661"/>
+  <dimension ref="A1:C1690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24221,6 +24221,424 @@
         <v>393</v>
       </c>
     </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr"/>
+      <c r="C1663" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr"/>
+      <c r="C1664" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr"/>
+      <c r="C1665" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr"/>
+      <c r="C1666" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr"/>
+      <c r="C1667" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr"/>
+      <c r="C1668" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weisbach e 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ernst abbe sportfeld
+  jena </t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="C1679" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr"/>
+      <c r="C1681" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>rFNN7oyi</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>AgnJojCs</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>CCww5Qfo</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1690"/>
+  <dimension ref="A1:C1691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24639,6 +24639,17 @@
         <v>268</v>
       </c>
     </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr"/>
+      <c r="C1691" t="n">
+        <v>397</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1691"/>
+  <dimension ref="A1:C1693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24650,6 +24650,38 @@
         <v>397</v>
       </c>
     </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1693"/>
+  <dimension ref="A1:C1695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24682,6 +24682,36 @@
         <v>99</v>
       </c>
     </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>398</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1695"/>
+  <dimension ref="A1:C1696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24712,6 +24712,21 @@
         <v>398</v>
       </c>
     </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>399</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1696"/>
+  <dimension ref="A1:C1697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24727,6 +24727,21 @@
         <v>399</v>
       </c>
     </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>WzqXh8OL</t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1697"/>
+  <dimension ref="A1:C1699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24742,6 +24742,36 @@
         <v>400</v>
       </c>
     </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1699"/>
+  <dimension ref="A1:C1705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24772,6 +24772,98 @@
         <v>401</v>
       </c>
     </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1266"/>
+  <dimension ref="A1:C1273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19456,6 +19456,118 @@
         <v>264</v>
       </c>
     </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1273"/>
+  <dimension ref="A1:C1275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19568,6 +19568,38 @@
         <v>93</v>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1275"/>
+  <dimension ref="A1:C1284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19600,6 +19600,143 @@
         <v>94</v>
       </c>
     </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1284"/>
+  <dimension ref="A1:C1285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19737,6 +19737,22 @@
         <v>95</v>
       </c>
     </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1285"/>
+  <dimension ref="A1:C1290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19753,6 +19753,84 @@
         <v>96</v>
       </c>
     </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">haslberger w 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>SMaB5LKo</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
